--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\ET_Branch\Excel\StartConfig\RouterTest\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC470956-B4CB-4A69-8FC6-28509B4A0553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -71,13 +65,33 @@
   </si>
   <si>
     <t>路由区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ET1000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号登录服</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>区分类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZoneType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -463,8 +477,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:F8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:G9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -474,12 +488,12 @@
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="F2" s="3" t="s">
+    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -487,13 +501,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -501,13 +518,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
@@ -515,44 +535,66 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="G5" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <v>3</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -85,6 +85,10 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ET2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -565,9 +569,13 @@
       <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G7" s="5" t="s">
         <v>13</v>
       </c>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -89,6 +89,22 @@
   </si>
   <si>
     <t>ET2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ET3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏1区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏2区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明New</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -96,7 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,8 +149,16 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,6 +169,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -177,6 +207,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G9"/>
+  <dimension ref="C2:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -492,12 +525,12 @@
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -513,8 +546,11 @@
       <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -530,8 +566,11 @@
       <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
@@ -547,8 +586,11 @@
       <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -564,46 +606,88 @@
       <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
         <v>1000</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
